--- a/exports/trend_1d/PAGEIND_full_report.xlsx
+++ b/exports/trend_1d/PAGEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.72</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>13413.45</v>
+        <v>12871.35</v>
       </c>
       <c r="I2" t="n">
         <v>13029.06528958181</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>22.95</v>
+        <v>17.98</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H3" t="n">
-        <v>13917.3</v>
+        <v>14641.65</v>
       </c>
       <c r="I3" t="n">
         <v>14428.93105379852</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.130000000000001</v>
+        <v>-13.75</v>
       </c>
       <c r="L3" t="n">
-        <v>10.7</v>
+        <v>14.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.69</v>
       </c>
       <c r="N3" t="n">
-        <v>3.96</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
         <v>-4.04</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42163</v>
+        <v>42164</v>
       </c>
       <c r="H4" t="n">
-        <v>14929.1</v>
+        <v>14577.65</v>
       </c>
       <c r="I4" t="n">
         <v>14621.79753262853</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>1.96</v>
+        <v>-0.44</v>
       </c>
       <c r="L4" t="n">
         <v>4.8</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42286</v>
+        <v>42289</v>
       </c>
       <c r="H5" t="n">
-        <v>14269.5</v>
+        <v>14657.1</v>
       </c>
       <c r="I5" t="n">
         <v>14518.88681289613</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K5" t="n">
-        <v>2.11</v>
+        <v>-0.55</v>
       </c>
       <c r="L5" t="n">
         <v>7.22</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>13473.15</v>
+        <v>13086.25</v>
       </c>
       <c r="I6" t="n">
         <v>13231.4115885603</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.08</v>
+        <v>-10.72</v>
       </c>
       <c r="L6" t="n">
-        <v>9.529999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.67</v>
       </c>
       <c r="N6" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
         <v>2.72</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42373</v>
+        <v>42374</v>
       </c>
       <c r="H7" t="n">
-        <v>13558.05</v>
+        <v>13828.55</v>
       </c>
       <c r="I7" t="n">
         <v>13567.87227323222</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.61</v>
+        <v>-5.67</v>
       </c>
       <c r="L7" t="n">
-        <v>5.84</v>
+        <v>5.95</v>
       </c>
       <c r="M7" t="n">
         <v>1.36</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>12645.35</v>
+        <v>12503.45</v>
       </c>
       <c r="I8" t="n">
         <v>12645.02707644112</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.56</v>
+        <v>-9.58</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>13.17</v>
       </c>
       <c r="M8" t="n">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
         <v>3.49</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42438</v>
+        <v>42439</v>
       </c>
       <c r="H9" t="n">
-        <v>11201.55</v>
+        <v>11412.45</v>
       </c>
       <c r="I9" t="n">
         <v>11222.37652479861</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K9" t="n">
-        <v>10.41</v>
+        <v>8.73</v>
       </c>
       <c r="L9" t="n">
         <v>2.77</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.86</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42585</v>
+        <v>42586</v>
       </c>
       <c r="H10" t="n">
-        <v>13962.35</v>
+        <v>13510.3</v>
       </c>
       <c r="I10" t="n">
         <v>13752.53865558541</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K10" t="n">
-        <v>22.34</v>
+        <v>18.38</v>
       </c>
       <c r="L10" t="n">
         <v>9.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42614</v>
+        <v>42615</v>
       </c>
       <c r="H11" t="n">
-        <v>15117.7</v>
+        <v>15235.35</v>
       </c>
       <c r="I11" t="n">
         <v>15207.46018897582</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.9</v>
+        <v>-12.77</v>
       </c>
       <c r="L11" t="n">
-        <v>12.51</v>
+        <v>13.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.44</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.9</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H12" t="n">
-        <v>16121.35</v>
+        <v>14976.7</v>
       </c>
       <c r="I12" t="n">
         <v>15157.74850829803</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" t="n">
-        <v>5.82</v>
+        <v>-1.7</v>
       </c>
       <c r="L12" t="n">
         <v>7.58</v>
@@ -1125,7 +1268,7 @@
         <v>3.02</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>7.1</v>
       </c>
       <c r="O12" t="n">
         <v>0.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>17.75</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42752</v>
+        <v>42753</v>
       </c>
       <c r="H13" t="n">
-        <v>14074.1</v>
+        <v>14486.1</v>
       </c>
       <c r="I13" t="n">
         <v>14486.0675229136</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" t="n">
-        <v>6.03</v>
+        <v>3.28</v>
       </c>
       <c r="L13" t="n">
         <v>9.470000000000001</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.83</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42838</v>
+        <v>42842</v>
       </c>
       <c r="H14" t="n">
-        <v>14052.6</v>
+        <v>13844.25</v>
       </c>
       <c r="I14" t="n">
         <v>13951.40611856163</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.99</v>
+        <v>-4.43</v>
       </c>
       <c r="L14" t="n">
         <v>5.36</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.83</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H15" t="n">
-        <v>14792.8</v>
+        <v>14833.35</v>
       </c>
       <c r="I15" t="n">
         <v>14796.61625308872</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.85</v>
+        <v>-7.14</v>
       </c>
       <c r="L15" t="n">
         <v>7.91</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H16" t="n">
-        <v>14413.2</v>
+        <v>14130.4</v>
       </c>
       <c r="I16" t="n">
         <v>14249.53668261323</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.83</v>
+        <v>-4.74</v>
       </c>
       <c r="L16" t="n">
         <v>6.69</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>11.34</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H17" t="n">
-        <v>14925.7</v>
+        <v>15609.4</v>
       </c>
       <c r="I17" t="n">
         <v>15472.46294979976</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.63</v>
+        <v>-10.47</v>
       </c>
       <c r="L17" t="n">
-        <v>8.630000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="M17" t="n">
         <v>7.12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.14</v>
+        <v>4.58</v>
       </c>
       <c r="O17" t="n">
         <v>-1.96</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43111</v>
+        <v>43112</v>
       </c>
       <c r="H18" t="n">
-        <v>22997.25</v>
+        <v>22750.9</v>
       </c>
       <c r="I18" t="n">
         <v>22795.27687724599</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K18" t="n">
-        <v>47.33</v>
+        <v>45.75</v>
       </c>
       <c r="L18" t="n">
         <v>4.87</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.66</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43140</v>
+        <v>43143</v>
       </c>
       <c r="H19" t="n">
-        <v>21398.95</v>
+        <v>22069.3</v>
       </c>
       <c r="I19" t="n">
         <v>21617.70517187453</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>5.94</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>1.97</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H20" t="n">
-        <v>33592.45</v>
+        <v>32621.2</v>
       </c>
       <c r="I20" t="n">
         <v>33216.01327355322</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K20" t="n">
-        <v>52.21</v>
+        <v>47.81</v>
       </c>
       <c r="L20" t="n">
         <v>8.92</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.73</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H21" t="n">
-        <v>23003.4</v>
+        <v>23833.25</v>
       </c>
       <c r="I21" t="n">
         <v>23752.22674464454</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K21" t="n">
-        <v>29.48</v>
+        <v>26.94</v>
       </c>
       <c r="L21" t="n">
         <v>5.66</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.47</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H22" t="n">
-        <v>23585.9</v>
+        <v>22907.8</v>
       </c>
       <c r="I22" t="n">
         <v>23047.94527297204</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.04</v>
+        <v>-3.88</v>
       </c>
       <c r="L22" t="n">
-        <v>3.38</v>
+        <v>4.42</v>
       </c>
       <c r="M22" t="n">
         <v>0.53</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43725</v>
+        <v>43726</v>
       </c>
       <c r="H23" t="n">
-        <v>19414.1</v>
+        <v>19788.75</v>
       </c>
       <c r="I23" t="n">
         <v>19485.87025309541</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K23" t="n">
-        <v>15.25</v>
+        <v>13.62</v>
       </c>
       <c r="L23" t="n">
         <v>3.68</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.39</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H24" t="n">
-        <v>23047.55</v>
+        <v>22180.2</v>
       </c>
       <c r="I24" t="n">
         <v>22362.3716909627</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47</v>
+        <v>12.08</v>
       </c>
       <c r="L24" t="n">
         <v>3.53</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43825</v>
+        <v>43826</v>
       </c>
       <c r="H25" t="n">
-        <v>22284.6</v>
+        <v>23534</v>
       </c>
       <c r="I25" t="n">
         <v>23493.0193476486</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.47</v>
+        <v>-6.1</v>
       </c>
       <c r="L25" t="n">
-        <v>3.71</v>
+        <v>7.18</v>
       </c>
       <c r="M25" t="n">
         <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>5.61</v>
       </c>
       <c r="O25" t="n">
         <v>-3.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H26" t="n">
-        <v>24437.75</v>
+        <v>23691.85</v>
       </c>
       <c r="I26" t="n">
         <v>24136.44696520381</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>3.84</v>
+        <v>0.67</v>
       </c>
       <c r="L26" t="n">
         <v>5.54</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.04</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H27" t="n">
-        <v>18866.4</v>
+        <v>19503.05</v>
       </c>
       <c r="I27" t="n">
         <v>19192.73609976135</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K27" t="n">
-        <v>20.37</v>
+        <v>17.68</v>
       </c>
       <c r="L27" t="n">
         <v>7.58</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.81</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43994</v>
+        <v>43997</v>
       </c>
       <c r="H28" t="n">
-        <v>18548.2</v>
+        <v>17775.65</v>
       </c>
       <c r="I28" t="n">
         <v>17870.78416984288</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.9</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>6.92</v>
+        <v>9.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.91</v>
       </c>
       <c r="N28" t="n">
-        <v>3.14</v>
+        <v>4.17</v>
       </c>
       <c r="O28" t="n">
         <v>3.37</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44005</v>
+        <v>44006</v>
       </c>
       <c r="H29" t="n">
-        <v>19177</v>
+        <v>20753.9</v>
       </c>
       <c r="I29" t="n">
         <v>20149.59228535748</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.88</v>
+        <v>-16.75</v>
       </c>
       <c r="L29" t="n">
-        <v>10.15</v>
+        <v>19.23</v>
       </c>
       <c r="M29" t="n">
         <v>0.72</v>
       </c>
       <c r="N29" t="n">
-        <v>7.06</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>-4.17</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>15.82</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H30" t="n">
-        <v>19163.05</v>
+        <v>18503.55</v>
       </c>
       <c r="I30" t="n">
         <v>18879.85666514741</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.67</v>
+        <v>-10.84</v>
       </c>
       <c r="L30" t="n">
-        <v>10.17</v>
+        <v>11.34</v>
       </c>
       <c r="M30" t="n">
         <v>0.74</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>14.69</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44099</v>
+        <v>44102</v>
       </c>
       <c r="H31" t="n">
-        <v>19700.3</v>
+        <v>20617.8</v>
       </c>
       <c r="I31" t="n">
         <v>20217.21520047077</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.47</v>
+        <v>-11.43</v>
       </c>
       <c r="L31" t="n">
-        <v>7.01</v>
+        <v>12</v>
       </c>
       <c r="M31" t="n">
         <v>0.9399999999999999</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.52</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H32" t="n">
-        <v>28928.65</v>
+        <v>27176.15</v>
       </c>
       <c r="I32" t="n">
         <v>27534.83188796786</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K32" t="n">
-        <v>40.31</v>
+        <v>31.81</v>
       </c>
       <c r="L32" t="n">
         <v>5.66</v>
@@ -2265,7 +2648,7 @@
         <v>2.36</v>
       </c>
       <c r="N32" t="n">
-        <v>3.77</v>
+        <v>6.06</v>
       </c>
       <c r="O32" t="n">
         <v>4.66</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>15.39</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H33" t="n">
-        <v>30302.1</v>
+        <v>31933.7</v>
       </c>
       <c r="I33" t="n">
         <v>30951.69372299238</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.5</v>
+        <v>-17.51</v>
       </c>
       <c r="L33" t="n">
-        <v>12.51</v>
+        <v>18.51</v>
       </c>
       <c r="M33" t="n">
         <v>1.74</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44421</v>
+        <v>44424</v>
       </c>
       <c r="H34" t="n">
-        <v>31183.45</v>
+        <v>30306.5</v>
       </c>
       <c r="I34" t="n">
         <v>31125.74339172387</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.35</v>
+        <v>-5.1</v>
       </c>
       <c r="L34" t="n">
         <v>14.62</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.71</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H35" t="n">
-        <v>32685.55</v>
+        <v>33152</v>
       </c>
       <c r="I35" t="n">
         <v>33090.42145371951</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.85</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>9.6</v>
+        <v>9.82</v>
       </c>
       <c r="M35" t="n">
         <v>0.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.02</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H36" t="n">
-        <v>42539.95</v>
+        <v>39915.6</v>
       </c>
       <c r="I36" t="n">
         <v>41741.44861674443</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K36" t="n">
-        <v>28.32</v>
+        <v>20.4</v>
       </c>
       <c r="L36" t="n">
         <v>4.79</v>
@@ -2493,7 +2924,7 @@
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.91</v>
+        <v>6.17</v>
       </c>
       <c r="O36" t="n">
         <v>1.43</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.55</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H37" t="n">
-        <v>43713</v>
+        <v>44332.85</v>
       </c>
       <c r="I37" t="n">
         <v>43747.05234982527</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.51</v>
+        <v>-11.07</v>
       </c>
       <c r="L37" t="n">
-        <v>10.73</v>
+        <v>11.41</v>
       </c>
       <c r="M37" t="n">
         <v>5.34</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.31</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H38" t="n">
-        <v>44911.5</v>
+        <v>42619.95</v>
       </c>
       <c r="I38" t="n">
         <v>42815.45274716686</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K38" t="n">
-        <v>1.31</v>
+        <v>-3.86</v>
       </c>
       <c r="L38" t="n">
-        <v>1.91</v>
+        <v>4.35</v>
       </c>
       <c r="M38" t="n">
         <v>0.76</v>
       </c>
       <c r="N38" t="n">
-        <v>2.31</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.67</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H39" t="n">
-        <v>45042.3</v>
+        <v>45194.05</v>
       </c>
       <c r="I39" t="n">
         <v>45094.42434422944</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.68</v>
+        <v>-6.04</v>
       </c>
       <c r="L39" t="n">
-        <v>6.51</v>
+        <v>8.09</v>
       </c>
       <c r="M39" t="n">
         <v>3.28</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.56</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H40" t="n">
-        <v>41346.65</v>
+        <v>40537.9</v>
       </c>
       <c r="I40" t="n">
         <v>40875.5280874021</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.51</v>
+        <v>-10.3</v>
       </c>
       <c r="L40" t="n">
-        <v>9.83</v>
+        <v>11.05</v>
       </c>
       <c r="M40" t="n">
         <v>0.88</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.85</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H41" t="n">
-        <v>42348.25</v>
+        <v>43570.9</v>
       </c>
       <c r="I41" t="n">
         <v>42488.40423200504</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.47</v>
+        <v>-7.48</v>
       </c>
       <c r="L41" t="n">
-        <v>5.07</v>
+        <v>7.98</v>
       </c>
       <c r="M41" t="n">
         <v>1.56</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.43</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H42" t="n">
-        <v>49581.45</v>
+        <v>48666</v>
       </c>
       <c r="I42" t="n">
         <v>48982.18923303675</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K42" t="n">
-        <v>13.79</v>
+        <v>11.69</v>
       </c>
       <c r="L42" t="n">
         <v>3.8</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H43" t="n">
-        <v>38019</v>
+        <v>39259.15</v>
       </c>
       <c r="I43" t="n">
         <v>38648.33901264145</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K43" t="n">
-        <v>21.88</v>
+        <v>19.33</v>
       </c>
       <c r="L43" t="n">
         <v>2.17</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.79</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="H44" t="n">
-        <v>41120.75</v>
+        <v>37501.3</v>
       </c>
       <c r="I44" t="n">
         <v>40311.1612208013</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K44" t="n">
-        <v>4.74</v>
+        <v>-4.48</v>
       </c>
       <c r="L44" t="n">
-        <v>2.95</v>
+        <v>10.97</v>
       </c>
       <c r="M44" t="n">
-        <v>0.35</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O44" t="n">
         <v>3.26</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.69</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45138</v>
+        <v>45139</v>
       </c>
       <c r="H45" t="n">
-        <v>37805.05</v>
+        <v>38701.55</v>
       </c>
       <c r="I45" t="n">
         <v>38169.1408247608</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.2</v>
       </c>
       <c r="L45" t="n">
         <v>5.74</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.3</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H46" t="n">
-        <v>39876.7</v>
+        <v>39519.9</v>
       </c>
       <c r="I46" t="n">
         <v>39531.18156431935</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K46" t="n">
-        <v>3.04</v>
+        <v>2.11</v>
       </c>
       <c r="L46" t="n">
         <v>2.16</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.33</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45292</v>
+        <v>45293</v>
       </c>
       <c r="H47" t="n">
-        <v>38773.45</v>
+        <v>39189.2</v>
       </c>
       <c r="I47" t="n">
         <v>39090.8007810066</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K47" t="n">
-        <v>1.89</v>
+        <v>0.84</v>
       </c>
       <c r="L47" t="n">
         <v>1.77</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.63</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H48" t="n">
-        <v>37693.4</v>
+        <v>36452.65</v>
       </c>
       <c r="I48" t="n">
         <v>36958.34720399211</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.82</v>
+        <v>-6.98</v>
       </c>
       <c r="L48" t="n">
-        <v>4.16</v>
+        <v>7.81</v>
       </c>
       <c r="M48" t="n">
         <v>0.14</v>
       </c>
       <c r="N48" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="O48" t="n">
         <v>1.07</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H49" t="n">
-        <v>35024.6</v>
+        <v>36331.7</v>
       </c>
       <c r="I49" t="n">
         <v>36288.97993160557</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K49" t="n">
-        <v>3.92</v>
+        <v>0.33</v>
       </c>
       <c r="L49" t="n">
         <v>9.07</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H50" t="n">
-        <v>34486.45</v>
+        <v>34356.85</v>
       </c>
       <c r="I50" t="n">
         <v>34361.97097985953</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.08</v>
+        <v>-5.44</v>
       </c>
       <c r="L50" t="n">
         <v>6.78</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.8</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H51" t="n">
-        <v>35554.9</v>
+        <v>36607.9</v>
       </c>
       <c r="I51" t="n">
         <v>36574.61213632459</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.49</v>
+        <v>-6.55</v>
       </c>
       <c r="L51" t="n">
-        <v>6.79</v>
+        <v>7.9</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H52" t="n">
-        <v>43441.6</v>
+        <v>43038.6</v>
       </c>
       <c r="I52" t="n">
         <v>43074.6604553109</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K52" t="n">
-        <v>18.67</v>
+        <v>17.57</v>
       </c>
       <c r="L52" t="n">
         <v>3.83</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>9.58</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="H53" t="n">
-        <v>45064.1</v>
+        <v>48002.9</v>
       </c>
       <c r="I53" t="n">
         <v>46246.31107194747</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.71</v>
+        <v>-11.53</v>
       </c>
       <c r="L53" t="n">
-        <v>5.7</v>
+        <v>12.3</v>
       </c>
       <c r="M53" t="n">
         <v>0.91</v>
       </c>
       <c r="N53" t="n">
-        <v>2.06</v>
+        <v>6.52</v>
       </c>
       <c r="O53" t="n">
         <v>-0.93</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.45</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H54" t="n">
-        <v>46745.55</v>
+        <v>45911.6</v>
       </c>
       <c r="I54" t="n">
         <v>46479.69884600776</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.62</v>
+        <v>-4.36</v>
       </c>
       <c r="L54" t="n">
         <v>8.4</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H55" t="n">
-        <v>42127.95</v>
+        <v>43127</v>
       </c>
       <c r="I55" t="n">
         <v>42777.26722481973</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K55" t="n">
-        <v>8.24</v>
+        <v>6.07</v>
       </c>
       <c r="L55" t="n">
         <v>5.42</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H56" t="n">
-        <v>45760</v>
+        <v>44865</v>
       </c>
       <c r="I56" t="n">
         <v>45629.00194099962</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K56" t="n">
-        <v>6.11</v>
+        <v>4.03</v>
       </c>
       <c r="L56" t="n">
         <v>5.92</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H57" t="n">
-        <v>34425</v>
+        <v>35640</v>
       </c>
       <c r="I57" t="n">
         <v>34831.63621578921</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K57" t="n">
-        <v>23.27</v>
+        <v>20.56</v>
       </c>
       <c r="L57" t="n">
         <v>5.45</v>
@@ -3690,7 +4373,7 @@
         <v>4.36</v>
       </c>
       <c r="N57" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="O57" t="n">
         <v>-1.96</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>7</v>
+      </c>
+      <c r="U57" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>10.38</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H58" t="n">
-        <v>32110</v>
+        <v>31175</v>
       </c>
       <c r="I58" t="n">
         <v>31941.91243856029</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>-9.9</v>
+        <v>-12.53</v>
       </c>
       <c r="L58" t="n">
-        <v>10.94</v>
+        <v>13.5</v>
       </c>
       <c r="M58" t="n">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="N58" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="O58" t="n">
         <v>3.53</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H59" t="n">
-        <v>32170</v>
+        <v>32635</v>
       </c>
       <c r="I59" t="n">
         <v>32400.55832320321</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.19</v>
+        <v>-4.68</v>
       </c>
       <c r="L59" t="n">
-        <v>4.25</v>
+        <v>7.3</v>
       </c>
       <c r="M59" t="n">
         <v>2.09</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.74</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H60" t="n">
-        <v>36245</v>
+        <v>35085</v>
       </c>
       <c r="I60" t="n">
         <v>35243.49804777276</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K60" t="n">
-        <v>11.06</v>
+        <v>7.51</v>
       </c>
       <c r="L60" t="n">
         <v>4.21</v>
@@ -3861,7 +4580,7 @@
         <v>0.98</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O60" t="n">
         <v>1.45</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="H61" t="n">
-        <v>37505</v>
+        <v>38700</v>
       </c>
       <c r="I61" t="n">
         <v>38013.1534243507</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.9</v>
+        <v>-10.3</v>
       </c>
       <c r="L61" t="n">
-        <v>7.14</v>
+        <v>10.73</v>
       </c>
       <c r="M61" t="n">
         <v>0.4</v>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>3.19</v>
       </c>
       <c r="O61" t="n">
         <v>-3.2</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.44</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H62" t="n">
-        <v>40615</v>
+        <v>39395</v>
       </c>
       <c r="I62" t="n">
         <v>39457.38310285484</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K62" t="n">
-        <v>4.95</v>
+        <v>1.8</v>
       </c>
       <c r="L62" t="n">
         <v>5.47</v>
@@ -3975,7 +4718,7 @@
         <v>0.68</v>
       </c>
       <c r="N62" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
         <v>3.19</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>11.71</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H63" t="n">
-        <v>35950</v>
+        <v>37150</v>
       </c>
       <c r="I63" t="n">
         <v>37041.53967934573</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K63" t="n">
-        <v>8.74</v>
+        <v>5.7</v>
       </c>
       <c r="L63" t="n">
         <v>5.57</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>9</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H64" t="n">
-        <v>35770</v>
+        <v>34870</v>
       </c>
       <c r="I64" t="n">
         <v>35165.16656871985</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.71</v>
+        <v>-6.14</v>
       </c>
       <c r="L64" t="n">
-        <v>4.31</v>
+        <v>6.3</v>
       </c>
       <c r="M64" t="n">
         <v>0.99</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>6</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9107,7 +9894,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.59999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="6">
@@ -9117,7 +9904,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9127,7 +9914,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -9137,7 +9924,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9147,7 +9934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10">
@@ -9157,7 +9944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149.6</v>
+        <v>150.6</v>
       </c>
     </row>
     <row r="11">
@@ -9167,7 +9954,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9177,7 +9964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -9187,7 +9974,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.7</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="14">
@@ -9197,7 +9984,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.47</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -9207,7 +9994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.29</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="16">
@@ -9217,7 +10004,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.56</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="17">
@@ -9227,7 +10014,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52.21</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="18">
@@ -9237,7 +10024,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="19">
@@ -9247,7 +10034,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.44</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="20">
@@ -9257,7 +10044,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.74</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="21">
@@ -9267,7 +10054,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.62</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="22">
@@ -9277,7 +10064,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -9287,7 +10074,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -9297,7 +10084,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="25">
@@ -9307,7 +10094,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9317,7 +10104,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.99</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="27">
@@ -9327,7 +10114,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.78</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -9337,7 +10124,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
